--- a/tests/data/o21.xlsx
+++ b/tests/data/o21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H814"/>
+  <dimension ref="A1:G814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,11 +464,6 @@
           <t>Section</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -506,11 +501,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>7569884882</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -548,11 +538,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>9490239314</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -590,11 +575,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>9542406788</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -632,11 +612,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>8121087108</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -674,11 +649,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>8985315030</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -716,11 +686,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>9989623652</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -758,11 +723,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>9989495669</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -800,11 +760,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>9398148108</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -842,11 +797,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>7075812307</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -884,11 +834,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>9701904493</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -926,11 +871,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>6302466151</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -968,11 +908,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>9866812741</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1010,11 +945,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>8985592859</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1052,11 +982,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>9963292522</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1094,11 +1019,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>9989495669</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1136,11 +1056,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>6300827459</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1178,11 +1093,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>8331812949</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1220,11 +1130,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>9000838544</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1262,11 +1167,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>9618479850</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1304,11 +1204,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>9100007888</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1346,11 +1241,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>9676985989</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1388,11 +1278,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>7729816196</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1430,11 +1315,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>9014270310</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1472,11 +1352,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>9182348465</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1514,11 +1389,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>9949949649</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1556,11 +1426,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>9666938739</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1598,11 +1463,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>9133506211</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1640,11 +1500,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>9573956623</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1682,11 +1537,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>9963279098</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1724,11 +1574,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>9989159724</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1766,11 +1611,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>8125553410</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1808,11 +1648,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1850,11 +1685,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>9581959324</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1892,11 +1722,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>8341995375</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1934,11 +1759,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>7893694879</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1976,11 +1796,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>9985808094</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2018,11 +1833,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>8978786139</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2060,11 +1870,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>9177097969</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2102,11 +1907,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>9985839210</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2144,11 +1944,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>7893353839</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2186,11 +1981,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>7893771224</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2228,11 +2018,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>8121565758</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2270,11 +2055,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>9848585856</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2312,11 +2092,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>9676304856</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2354,11 +2129,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>9866704369</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2396,11 +2166,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>9866815132</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2438,11 +2203,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>9885247800</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2480,11 +2240,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>9440396627</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2522,11 +2277,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>9492089650</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2564,11 +2314,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>6301737284</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2606,11 +2351,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>9000974467</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2648,11 +2388,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>9441176628</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2690,11 +2425,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>8985518100</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2732,11 +2462,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>9392869437</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2774,11 +2499,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>9573838078</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2816,11 +2536,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>9701071892</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2858,11 +2573,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>9505087379</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2900,11 +2610,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>9948970348</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2942,11 +2647,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>9014562118</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2984,11 +2684,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>9502045587</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3026,11 +2721,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>9959185907</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3068,11 +2758,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>9247832836</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3110,11 +2795,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>9573028856</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3152,11 +2832,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>9704179626</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3194,11 +2869,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>9010222980</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3236,11 +2906,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>8374187311</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3278,11 +2943,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>9912576341</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3320,11 +2980,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>9491705350</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3362,11 +3017,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>8247349419</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3404,11 +3054,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>8978384213</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3446,11 +3091,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>9849736616</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3488,11 +3128,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>7729922162</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3530,11 +3165,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>9177375366</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3572,11 +3202,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>9704812832</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3614,11 +3239,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>9391799692</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3656,11 +3276,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>9000543441</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3698,11 +3313,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>9963287169</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3740,11 +3350,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>8555934569</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3782,11 +3387,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>9640003677</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3824,11 +3424,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>9866433188</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3866,11 +3461,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>8185972316</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3908,11 +3498,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>9652861561</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3950,11 +3535,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>9502674057</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3992,11 +3572,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>7330789605</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4034,11 +3609,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>9347596935</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4076,11 +3646,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>9640181345</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4118,11 +3683,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>9502251063</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4160,11 +3720,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>8985100457</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4202,11 +3757,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>9550151206</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4244,11 +3794,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>9908995426</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4286,11 +3831,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>6300425123</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4328,11 +3868,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>6303482305</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4370,11 +3905,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>9951072564</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4412,11 +3942,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>7013019418</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4454,11 +3979,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>8464855772</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4496,11 +4016,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>9059124297</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4538,11 +4053,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>9398867482</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4580,11 +4090,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>9912513426</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4622,11 +4127,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>7287828767</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4664,11 +4164,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>9704437255</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4706,11 +4201,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>9912042912</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4748,11 +4238,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>9346475893</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4790,11 +4275,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>8500065024</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4832,11 +4312,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>8919604781</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4874,11 +4349,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>8919411462</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4916,11 +4386,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>9866559566</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4958,11 +4423,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>7569985109</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5000,11 +4460,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>7893578501</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5042,11 +4497,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>9441412453</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5084,11 +4534,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>8897829075</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5126,11 +4571,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>9490384069</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5168,11 +4608,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>9949770973</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5210,11 +4645,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>6303760559</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5252,11 +4682,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>9502527493</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5294,11 +4719,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>9490272712</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5336,11 +4756,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>7729913609</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5378,11 +4793,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>7794969763</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5420,11 +4830,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>9441239205</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5462,11 +4867,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>9640015408</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5504,11 +4904,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>9390139980</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5546,11 +4941,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>9676344623</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5588,11 +4978,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>9573735645</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5630,11 +5015,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>9494088043</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5672,11 +5052,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>9959695398</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5714,11 +5089,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>9440017713</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5756,11 +5126,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>9059596630</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5798,11 +5163,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>9948499026</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5840,11 +5200,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>9849951075</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5882,11 +5237,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>8328598521</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5924,11 +5274,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>6303117706</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5966,11 +5311,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>8019999423</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6008,11 +5348,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>7989962682</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6050,11 +5385,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>9010309366</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6092,11 +5422,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>9948887495</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6134,11 +5459,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>9951944736</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6176,11 +5496,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>9247203995</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6218,11 +5533,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>9059828487</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6260,11 +5570,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>9949618982</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6302,11 +5607,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>9676210063</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6344,11 +5644,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>9642468765</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6386,11 +5681,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>8309399696</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6428,11 +5718,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>8499831973</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6470,11 +5755,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>7702292521</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6512,11 +5792,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>9542452088</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6554,11 +5829,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>9000121445</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6596,11 +5866,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>9959276956</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6638,11 +5903,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>7382904246</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6680,11 +5940,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>9052618511</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6722,11 +5977,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>8499918023</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6764,11 +6014,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>7675064337</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6806,11 +6051,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>9704928441</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6848,11 +6088,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>8374841292</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6890,11 +6125,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>8555008537</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6932,11 +6162,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>9490429917</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6974,11 +6199,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>9966571710</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7016,11 +6236,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>7036670737</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7058,11 +6273,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>9294002647</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7100,11 +6310,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>9502215148</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7142,11 +6347,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>8096016978</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7184,11 +6384,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>8125823724</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7226,11 +6421,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>9849915079</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7268,11 +6458,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>9440765285</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7310,11 +6495,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>9949131474</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7352,11 +6532,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>9010524162</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7394,11 +6569,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>7095767635</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7436,11 +6606,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>7995873447</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7478,11 +6643,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>6304976971</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7520,11 +6680,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>9849594547</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7562,11 +6717,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>9948892548</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7604,11 +6754,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>9848337656</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7646,11 +6791,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>9441172113</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7688,11 +6828,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>9951312648</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7730,11 +6865,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>9014857872</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7772,11 +6902,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>9573243649</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7814,11 +6939,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>8639297884</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7856,11 +6976,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>8367329266</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7898,11 +7013,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>8309213693</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7940,11 +7050,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>9912993994</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7982,11 +7087,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>9951658070</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8024,11 +7124,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>9949539737</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8066,11 +7161,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>9666215838</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8108,11 +7198,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>8187818369</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8150,11 +7235,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>9959829379</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8192,11 +7272,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>9347832604</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8234,11 +7309,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>7981729323</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8276,11 +7346,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>8500414805</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8318,11 +7383,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>9848449481</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8360,11 +7420,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>8555079502</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8402,11 +7457,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>7893833370</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8444,11 +7494,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>9666129486</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8486,7 +7531,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8524,11 +7568,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>9704241735</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8566,11 +7605,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>9392004930</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8608,11 +7642,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>7997952726</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8650,11 +7679,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>9492276874</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8692,11 +7716,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>8143632835</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8734,11 +7753,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>9985310202</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8776,11 +7790,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>9701688785</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8818,11 +7827,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>7396150888</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8860,11 +7864,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>9177680106</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8902,11 +7901,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>9133231146</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8944,11 +7938,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>9652854082</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8986,11 +7975,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>9492316578</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9028,11 +8012,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>8500856720</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9070,11 +8049,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>9866909746</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9112,11 +8086,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>8106450166</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9154,11 +8123,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>9848446810</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -9196,11 +8160,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>9492759501</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -9238,11 +8197,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>9014117116</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -9280,11 +8234,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>9985735877</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -9322,7 +8271,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -9360,11 +8308,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>9866737305</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -9402,11 +8345,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>9848531669</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9444,11 +8382,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>9032089176</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9486,11 +8419,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>8919576689</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9528,11 +8456,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>9618541219</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9570,11 +8493,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>9948449798</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9612,11 +8530,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>8985352993</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9654,11 +8567,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>9701487396</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9696,11 +8604,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>994977966</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9738,11 +8641,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>8074284891</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9780,11 +8678,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>9441088199</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9822,11 +8715,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>9492517280</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9864,11 +8752,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>9704109417</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9906,11 +8789,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>9100453824</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9948,11 +8826,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>9989221022</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9990,11 +8863,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>9866447970</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -10032,11 +8900,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>8096321881</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -10074,11 +8937,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>9704744798</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -10116,11 +8974,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>9441414744</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -10158,11 +9011,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>9381506813</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -10200,11 +9048,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>9705488155</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -10242,11 +9085,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>7730847576</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -10284,11 +9122,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>8332821239</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10326,11 +9159,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>9703265772</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -10368,11 +9196,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>6300724230</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -10410,11 +9233,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>9441849613</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -10452,11 +9270,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>7382892329</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -10494,11 +9307,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>7893975258</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10536,11 +9344,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>9652208424</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10578,11 +9381,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>6302281743</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10620,11 +9418,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>9951695626</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10662,11 +9455,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>9100517400</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10704,11 +9492,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>7013489701</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10746,11 +9529,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>9912613621</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10788,11 +9566,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>9246610004</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10830,11 +9603,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>8500372975</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10872,11 +9640,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>8008965857</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10914,11 +9677,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>9553801394</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10956,11 +9714,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>7893532668</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10998,11 +9751,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>8096772371</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -11040,11 +9788,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>9491276039</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -11082,11 +9825,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>9949921494</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -11124,11 +9862,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>9440635938</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -11166,11 +9899,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>7093355638</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -11208,11 +9936,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>9000060020</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -11250,11 +9973,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>9347749274</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -11292,11 +10010,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>9704088662</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -11334,11 +10047,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>9642338089</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -11376,11 +10084,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>8247527556</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -11418,11 +10121,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>9640306174</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -11460,11 +10158,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>7032525264</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -11502,11 +10195,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>9885090565</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -11544,11 +10232,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>9346167064</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11586,11 +10269,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>8185837277</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11628,11 +10306,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>9391411089</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11670,11 +10343,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>9963186739</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11712,11 +10380,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>7337551498</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11754,11 +10417,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>9542901971</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -11796,11 +10454,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>9618945627</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -11838,11 +10491,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>9949124151</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -11880,11 +10528,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>6303336908</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -11922,11 +10565,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>9908102213</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -11964,11 +10602,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>7013044468</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -12006,11 +10639,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>9912649365</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -12048,11 +10676,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>9963183532</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -12090,11 +10713,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>7893433990</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -12132,11 +10750,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>7729804586</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -12174,11 +10787,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>9491237064</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -12216,11 +10824,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>9640943882</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -12258,11 +10861,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>9542463873</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -12300,11 +10898,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>9618854852</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -12342,11 +10935,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>7569297722</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -12384,11 +10972,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>9100310200</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -12426,11 +11009,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>7893624759</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -12468,11 +11046,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>9866277213</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -12510,11 +11083,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>9966680771</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -12552,11 +11120,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>7997427242</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -12594,11 +11157,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>7893491899</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -12636,11 +11194,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>9885259080</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -12678,11 +11231,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>9948054389</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12720,11 +11268,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>9550117338</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -12762,11 +11305,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>9701070171</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -12804,11 +11342,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>9505729461</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -12846,11 +11379,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>6301793668</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -12888,11 +11416,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>9705449287</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -12930,11 +11453,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>9542852431</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -12972,11 +11490,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>6305904854</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -13014,11 +11527,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>7093998927</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -13056,11 +11564,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>9908290250</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -13098,11 +11601,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>8008803735</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -13140,11 +11638,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>9985589370</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -13182,11 +11675,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>9492523223</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -13224,11 +11712,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>8008362553</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -13266,11 +11749,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>6300565721</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -13308,11 +11786,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>8367223797</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -13350,11 +11823,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>9581023809</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -13392,11 +11860,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>8106939711</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -13434,11 +11897,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>8985363462</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -13476,11 +11934,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>9619440331</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -13518,11 +11971,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>9618343120</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -13560,11 +12008,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>6305312714</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -13602,11 +12045,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>960341578</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -13644,11 +12082,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>8978914247</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -13686,11 +12119,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>9000412466</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -13728,11 +12156,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>7981996418</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -13770,11 +12193,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>9032833417</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -13812,11 +12230,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>8074522294</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -13854,11 +12267,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>9676747989</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -13896,11 +12304,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>7702327013</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -13938,11 +12341,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>9010771300</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -13980,11 +12378,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>9441624323</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -14022,11 +12415,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>9010771201</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -14064,11 +12452,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>9492467335</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -14106,11 +12489,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>9177589002</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -14148,11 +12526,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>7416427907</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -14190,11 +12563,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>9346857205</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -14232,11 +12600,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>8074269869</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -14274,11 +12637,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>9618025132</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -14316,11 +12674,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>9182977902</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -14358,11 +12711,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>8978974526</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -14400,11 +12748,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>9000103194</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -14442,11 +12785,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>9440752020</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -14484,11 +12822,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>9959993931</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -14526,11 +12859,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>9000406649</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -14568,11 +12896,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>7013323001</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -14610,11 +12933,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>6304408964</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -14652,11 +12970,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>6302783024</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -14694,11 +13007,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>9700629574</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -14736,11 +13044,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>9963275265</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -14778,11 +13081,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>9912224622</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -14820,11 +13118,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>9908456775</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -14862,11 +13155,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>9848228492</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -14904,11 +13192,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>9491955468</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -14946,11 +13229,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>9441141012</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -14988,11 +13266,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>9493258936</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -15030,11 +13303,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>8374772500</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -15072,11 +13340,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>8096666520</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -15114,11 +13377,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>8978441761</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -15156,11 +13414,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>9949913930</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -15198,11 +13451,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>9441105457</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -15240,11 +13488,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>9295950800</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -15282,11 +13525,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>7659019169</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -15324,11 +13562,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>8977786233</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -15366,11 +13599,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>9347253171</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -15408,11 +13636,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>7095663066</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -15450,11 +13673,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>9441618039</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -15492,11 +13710,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>9441386287</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -15534,11 +13747,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>9502140750</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -15576,11 +13784,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>7032620648</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -15618,11 +13821,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>9398069807</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -15660,11 +13858,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>9440274966</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -15702,11 +13895,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>9676343433</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -15744,11 +13932,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>8374633577</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -15786,11 +13969,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>9704417089</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -15828,11 +14006,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>8639817382</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -15870,11 +14043,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>7702432340</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -15912,11 +14080,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>9866755845</t>
-        </is>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -15954,11 +14117,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
-        <is>
-          <t>7981558957</t>
-        </is>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -15996,11 +14154,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
-        <is>
-          <t>9491755257</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -16038,11 +14191,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>8978226242</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -16080,11 +14228,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>7993731908</t>
-        </is>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -16122,11 +14265,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>7730050182</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -16164,11 +14302,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>9490124064</t>
-        </is>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -16206,11 +14339,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr">
-        <is>
-          <t>9573966164</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -16248,11 +14376,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>9963265040</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -16290,11 +14413,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr">
-        <is>
-          <t>9391798015</t>
-        </is>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -16332,11 +14450,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
-        <is>
-          <t>9989232796</t>
-        </is>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -16374,11 +14487,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>9676283665</t>
-        </is>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -16416,11 +14524,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>9493707993</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -16458,11 +14561,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>9030666348</t>
-        </is>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -16500,11 +14598,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
-        <is>
-          <t>6305384814</t>
-        </is>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -16542,11 +14635,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr">
-        <is>
-          <t>9742542741998930000</t>
-        </is>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -16584,11 +14672,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
-        <is>
-          <t>9948393223</t>
-        </is>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -16626,11 +14709,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>8367084768</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -16668,11 +14746,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>9502887746</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -16710,11 +14783,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
-        <is>
-          <t>7287063934</t>
-        </is>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -16752,11 +14820,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>6301578703</t>
-        </is>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -16794,11 +14857,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>9441551254</t>
-        </is>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -16836,11 +14894,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>9494997397</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -16878,11 +14931,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>9000709635</t>
-        </is>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -16920,11 +14968,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>6281228593</t>
-        </is>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -16962,11 +15005,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>9441243057</t>
-        </is>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -17004,11 +15042,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>9347576802</t>
-        </is>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -17046,11 +15079,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>9866573540</t>
-        </is>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -17088,11 +15116,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>9949645874</t>
-        </is>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -17130,11 +15153,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>7270832845</t>
-        </is>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -17172,11 +15190,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>7288908650</t>
-        </is>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -17214,11 +15227,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr">
-        <is>
-          <t>9963175602</t>
-        </is>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -17256,11 +15264,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>9491338390</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -17298,11 +15301,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>9676630720</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -17340,11 +15338,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>9849589633</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -17382,11 +15375,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>8184846125</t>
-        </is>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -17424,11 +15412,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr">
-        <is>
-          <t>9553255777</t>
-        </is>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -17466,11 +15449,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>6305665115</t>
-        </is>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -17508,11 +15486,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>9490179969</t>
-        </is>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -17550,11 +15523,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr">
-        <is>
-          <t>9177713824</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -17592,11 +15560,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr">
-        <is>
-          <t>9059671192</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -17634,11 +15597,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>8125614115</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -17676,11 +15634,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>9705627856</t>
-        </is>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -17718,11 +15671,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>9160436350</t>
-        </is>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -17760,11 +15708,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>8121624224</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -17802,11 +15745,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>7981646972</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -17844,11 +15782,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>9347471911</t>
-        </is>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -17886,11 +15819,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>8886439620</t>
-        </is>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -17928,11 +15856,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>9848463181</t>
-        </is>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -17970,11 +15893,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>7702944231</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -18012,11 +15930,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>9100202588</t>
-        </is>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -18054,11 +15967,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>8639049010</t>
-        </is>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -18096,11 +16004,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>9989771881</t>
-        </is>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -18138,11 +16041,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>8790700515</t>
-        </is>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -18180,11 +16078,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>8247023235</t>
-        </is>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -18222,11 +16115,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>8978703798</t>
-        </is>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -18264,11 +16152,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>9640607964</t>
-        </is>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -18306,11 +16189,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>9963921546</t>
-        </is>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -18348,11 +16226,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>7013475767</t>
-        </is>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -18390,11 +16263,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>9441072663</t>
-        </is>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -18432,11 +16300,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr">
-        <is>
-          <t>8919121162</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -18474,11 +16337,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H430" t="inlineStr">
-        <is>
-          <t>9502285757</t>
-        </is>
-      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -18516,11 +16374,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H431" t="inlineStr">
-        <is>
-          <t>84659093896</t>
-        </is>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -18558,11 +16411,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr">
-        <is>
-          <t>7997869076</t>
-        </is>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -18600,11 +16448,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>9963370822</t>
-        </is>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -18642,11 +16485,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>9543845770</t>
-        </is>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -18684,11 +16522,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>6301493579</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -18726,11 +16559,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr">
-        <is>
-          <t>9705727808</t>
-        </is>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -18768,11 +16596,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
-        <is>
-          <t>9052656111</t>
-        </is>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -18810,11 +16633,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>9948260920</t>
-        </is>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -18852,11 +16670,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>9440522537</t>
-        </is>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -18894,11 +16707,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>8186909197</t>
-        </is>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -18936,11 +16744,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>8374479051</t>
-        </is>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -18978,11 +16781,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>9347130408</t>
-        </is>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -19020,11 +16818,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>9553402448</t>
-        </is>
-      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -19062,11 +16855,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>7286885815</t>
-        </is>
-      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -19104,11 +16892,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>8985818717</t>
-        </is>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -19146,11 +16929,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>8897867678</t>
-        </is>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -19188,11 +16966,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>8790007555</t>
-        </is>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -19230,11 +17003,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H448" t="inlineStr">
-        <is>
-          <t>9666515808</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -19272,11 +17040,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>9908736962</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -19314,11 +17077,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>9951561799</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -19356,11 +17114,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>9885371728</t>
-        </is>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -19398,11 +17151,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>9542479406</t>
-        </is>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -19440,11 +17188,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H453" t="inlineStr">
-        <is>
-          <t>9866737006</t>
-        </is>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -19482,11 +17225,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H454" t="inlineStr">
-        <is>
-          <t>8019820287</t>
-        </is>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -19524,11 +17262,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>7013813934</t>
-        </is>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -19566,11 +17299,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr">
-        <is>
-          <t>9704257254</t>
-        </is>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -19608,11 +17336,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H457" t="inlineStr">
-        <is>
-          <t>9160262367</t>
-        </is>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -19650,11 +17373,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>9618712368</t>
-        </is>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -19692,11 +17410,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr">
-        <is>
-          <t>7093912127</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -19734,11 +17447,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>9014186348</t>
-        </is>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -19776,11 +17484,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H461" t="inlineStr">
-        <is>
-          <t>9640097693</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -19818,11 +17521,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H462" t="inlineStr">
-        <is>
-          <t>9177286144</t>
-        </is>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -19860,11 +17558,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H463" t="inlineStr">
-        <is>
-          <t>9177375366</t>
-        </is>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -19902,11 +17595,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H464" t="inlineStr">
-        <is>
-          <t>8125619619</t>
-        </is>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -19944,11 +17632,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H465" t="inlineStr">
-        <is>
-          <t>9849068483</t>
-        </is>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -19986,11 +17669,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H466" t="inlineStr">
-        <is>
-          <t>7981360240</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -20028,11 +17706,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H467" t="inlineStr">
-        <is>
-          <t>7997699322</t>
-        </is>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -20070,11 +17743,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr">
-        <is>
-          <t>8897628249</t>
-        </is>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -20112,11 +17780,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H469" t="inlineStr">
-        <is>
-          <t>8978333946</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -20154,11 +17817,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H470" t="inlineStr">
-        <is>
-          <t>6302785747</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -20196,11 +17854,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H471" t="inlineStr">
-        <is>
-          <t>9949330853</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -20238,7 +17891,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -20276,11 +17928,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H473" t="inlineStr">
-        <is>
-          <t>9666481969</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -20318,11 +17965,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr">
-        <is>
-          <t>6309937493</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -20360,11 +18002,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H475" t="inlineStr">
-        <is>
-          <t>9989469984</t>
-        </is>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -20402,11 +18039,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H476" t="inlineStr">
-        <is>
-          <t>8897205455</t>
-        </is>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -20444,11 +18076,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H477" t="inlineStr">
-        <is>
-          <t>9248888817</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -20486,11 +18113,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H478" t="inlineStr">
-        <is>
-          <t>9959390475</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -20528,11 +18150,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H479" t="inlineStr">
-        <is>
-          <t>6304519850</t>
-        </is>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -20570,11 +18187,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H480" t="inlineStr">
-        <is>
-          <t>9848942090</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -20612,11 +18224,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H481" t="inlineStr">
-        <is>
-          <t>9381018954</t>
-        </is>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -20654,11 +18261,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H482" t="inlineStr">
-        <is>
-          <t>9553017965</t>
-        </is>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -20696,11 +18298,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H483" t="inlineStr">
-        <is>
-          <t>9100269098</t>
-        </is>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -20738,11 +18335,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr">
-        <is>
-          <t>9505352343</t>
-        </is>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -20780,11 +18372,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>9989865832</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -20822,11 +18409,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr">
-        <is>
-          <t>9963247940</t>
-        </is>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -20864,11 +18446,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>9949615860</t>
-        </is>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -20906,11 +18483,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr">
-        <is>
-          <t>9573347374</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -20948,11 +18520,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H489" t="inlineStr">
-        <is>
-          <t>7730963575</t>
-        </is>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -20990,11 +18557,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr">
-        <is>
-          <t>9908463581</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -21032,11 +18594,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H491" t="inlineStr">
-        <is>
-          <t>8500459148</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -21074,11 +18631,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr">
-        <is>
-          <t>7659899465</t>
-        </is>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -21116,11 +18668,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr">
-        <is>
-          <t>7780595624</t>
-        </is>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -21158,11 +18705,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H494" t="inlineStr">
-        <is>
-          <t>9292851555</t>
-        </is>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -21200,11 +18742,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H495" t="inlineStr">
-        <is>
-          <t>9676964008</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -21242,11 +18779,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t>9502265034</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -21284,11 +18816,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t>7032024503</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -21326,11 +18853,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr">
-        <is>
-          <t>9490496337</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -21368,11 +18890,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr">
-        <is>
-          <t>9652459006</t>
-        </is>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -21410,11 +18927,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr">
-        <is>
-          <t>9963635236</t>
-        </is>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -21452,11 +18964,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t>7893718657</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -21494,11 +19001,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H502" t="inlineStr">
-        <is>
-          <t>6281436385</t>
-        </is>
-      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -21536,11 +19038,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H503" t="inlineStr">
-        <is>
-          <t>9490330357</t>
-        </is>
-      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -21578,11 +19075,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr">
-        <is>
-          <t>9849866054</t>
-        </is>
-      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -21620,11 +19112,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H505" t="inlineStr">
-        <is>
-          <t>9640125427</t>
-        </is>
-      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -21662,11 +19149,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H506" t="inlineStr">
-        <is>
-          <t>9398135893</t>
-        </is>
-      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -21704,11 +19186,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H507" t="inlineStr">
-        <is>
-          <t>9515952134</t>
-        </is>
-      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -21746,11 +19223,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H508" t="inlineStr">
-        <is>
-          <t>9963231744</t>
-        </is>
-      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -21788,11 +19260,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H509" t="inlineStr">
-        <is>
-          <t>9666732907</t>
-        </is>
-      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -21830,11 +19297,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H510" t="inlineStr">
-        <is>
-          <t>9553380109</t>
-        </is>
-      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -21872,11 +19334,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr">
-        <is>
-          <t>9640325364</t>
-        </is>
-      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -21914,11 +19371,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H512" t="inlineStr">
-        <is>
-          <t>7095293941</t>
-        </is>
-      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -21956,11 +19408,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr">
-        <is>
-          <t>9491808479</t>
-        </is>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -21998,11 +19445,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H514" t="inlineStr">
-        <is>
-          <t>9951849475</t>
-        </is>
-      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -22040,11 +19482,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H515" t="inlineStr">
-        <is>
-          <t>7032493920</t>
-        </is>
-      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -22082,11 +19519,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H516" t="inlineStr">
-        <is>
-          <t>9491320420</t>
-        </is>
-      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -22124,11 +19556,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H517" t="inlineStr">
-        <is>
-          <t>9032221957</t>
-        </is>
-      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -22166,11 +19593,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H518" t="inlineStr">
-        <is>
-          <t>9989657740</t>
-        </is>
-      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -22208,11 +19630,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H519" t="inlineStr">
-        <is>
-          <t>9441306408</t>
-        </is>
-      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -22250,11 +19667,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H520" t="inlineStr">
-        <is>
-          <t>6305907706</t>
-        </is>
-      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -22292,11 +19704,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr">
-        <is>
-          <t>6301354623</t>
-        </is>
-      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -22334,11 +19741,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H522" t="inlineStr">
-        <is>
-          <t>9908147431</t>
-        </is>
-      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -22376,11 +19778,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr">
-        <is>
-          <t>9849644503</t>
-        </is>
-      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -22418,11 +19815,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>8142300899</t>
-        </is>
-      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -22460,11 +19852,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>9550852716</t>
-        </is>
-      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -22502,11 +19889,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr">
-        <is>
-          <t>8019940070</t>
-        </is>
-      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -22544,11 +19926,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H527" t="inlineStr">
-        <is>
-          <t>7702994055</t>
-        </is>
-      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -22586,11 +19963,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>9133289324</t>
-        </is>
-      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -22628,11 +20000,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H529" t="inlineStr">
-        <is>
-          <t>9182663488</t>
-        </is>
-      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -22670,11 +20037,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H530" t="inlineStr">
-        <is>
-          <t>9502482547</t>
-        </is>
-      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -22712,11 +20074,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H531" t="inlineStr">
-        <is>
-          <t>9849259608</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -22754,11 +20111,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H532" t="inlineStr">
-        <is>
-          <t>8106998090</t>
-        </is>
-      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -22796,11 +20148,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H533" t="inlineStr">
-        <is>
-          <t>6304237177</t>
-        </is>
-      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -22838,11 +20185,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H534" t="inlineStr">
-        <is>
-          <t>9492110721</t>
-        </is>
-      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -22880,11 +20222,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H535" t="inlineStr">
-        <is>
-          <t>7075390555</t>
-        </is>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -22922,11 +20259,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H536" t="inlineStr">
-        <is>
-          <t>9550427567</t>
-        </is>
-      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -22964,11 +20296,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H537" t="inlineStr">
-        <is>
-          <t>8639043500</t>
-        </is>
-      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -23006,11 +20333,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H538" t="inlineStr">
-        <is>
-          <t>7396515147</t>
-        </is>
-      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -23048,11 +20370,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr">
-        <is>
-          <t>9885108802</t>
-        </is>
-      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -23090,11 +20407,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H540" t="inlineStr">
-        <is>
-          <t>7095383795</t>
-        </is>
-      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -23132,11 +20444,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H541" t="inlineStr">
-        <is>
-          <t>9441916081</t>
-        </is>
-      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -23174,11 +20481,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H542" t="inlineStr">
-        <is>
-          <t>9640392581</t>
-        </is>
-      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -23216,11 +20518,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H543" t="inlineStr">
-        <is>
-          <t>9491582792</t>
-        </is>
-      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -23258,11 +20555,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H544" t="inlineStr">
-        <is>
-          <t>9985382683</t>
-        </is>
-      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -23300,11 +20592,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H545" t="inlineStr">
-        <is>
-          <t>9966591688</t>
-        </is>
-      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -23342,11 +20629,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H546" t="inlineStr">
-        <is>
-          <t>9381267740</t>
-        </is>
-      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -23384,11 +20666,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H547" t="inlineStr">
-        <is>
-          <t>9705621823</t>
-        </is>
-      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -23426,11 +20703,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H548" t="inlineStr">
-        <is>
-          <t>9603545915</t>
-        </is>
-      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -23468,11 +20740,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H549" t="inlineStr">
-        <is>
-          <t>9502299084</t>
-        </is>
-      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -23510,11 +20777,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H550" t="inlineStr">
-        <is>
-          <t>9390455471</t>
-        </is>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -23552,11 +20814,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H551" t="inlineStr">
-        <is>
-          <t>9966558557</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -23594,11 +20851,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H552" t="inlineStr">
-        <is>
-          <t>9542437942</t>
-        </is>
-      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -23636,11 +20888,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H553" t="inlineStr">
-        <is>
-          <t>9490041335</t>
-        </is>
-      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -23678,11 +20925,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H554" t="inlineStr">
-        <is>
-          <t>8500343196</t>
-        </is>
-      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -23720,11 +20962,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H555" t="inlineStr">
-        <is>
-          <t>9441006053</t>
-        </is>
-      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -23762,11 +20999,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H556" t="inlineStr">
-        <is>
-          <t>7801094780</t>
-        </is>
-      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -23804,11 +21036,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H557" t="inlineStr">
-        <is>
-          <t>9959446395</t>
-        </is>
-      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -23846,11 +21073,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H558" t="inlineStr">
-        <is>
-          <t>9908375901</t>
-        </is>
-      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -23888,11 +21110,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H559" t="inlineStr">
-        <is>
-          <t>9573736632</t>
-        </is>
-      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -23930,11 +21147,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H560" t="inlineStr">
-        <is>
-          <t>8008623072</t>
-        </is>
-      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -23972,11 +21184,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H561" t="inlineStr">
-        <is>
-          <t>9441937253</t>
-        </is>
-      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -24014,11 +21221,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H562" t="inlineStr">
-        <is>
-          <t>9959353964</t>
-        </is>
-      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -24056,11 +21258,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H563" t="inlineStr">
-        <is>
-          <t>9542348679</t>
-        </is>
-      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -24098,11 +21295,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr">
-        <is>
-          <t>8328336837</t>
-        </is>
-      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -24140,11 +21332,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H565" t="inlineStr">
-        <is>
-          <t>9705037841</t>
-        </is>
-      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -24182,11 +21369,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H566" t="inlineStr">
-        <is>
-          <t>9553137041</t>
-        </is>
-      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -24224,11 +21406,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H567" t="inlineStr">
-        <is>
-          <t>9989783632</t>
-        </is>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -24266,11 +21443,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H568" t="inlineStr">
-        <is>
-          <t>9885125212</t>
-        </is>
-      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -24308,11 +21480,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H569" t="inlineStr">
-        <is>
-          <t>7095711856</t>
-        </is>
-      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -24350,11 +21517,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H570" t="inlineStr">
-        <is>
-          <t>6305758776</t>
-        </is>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -24392,11 +21554,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H571" t="inlineStr">
-        <is>
-          <t>6305096723</t>
-        </is>
-      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -24434,11 +21591,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H572" t="inlineStr">
-        <is>
-          <t>9515063744</t>
-        </is>
-      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -24476,11 +21628,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H573" t="inlineStr">
-        <is>
-          <t>9703643920</t>
-        </is>
-      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -24518,11 +21665,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H574" t="inlineStr">
-        <is>
-          <t>9390610092</t>
-        </is>
-      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -24560,11 +21702,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H575" t="inlineStr">
-        <is>
-          <t>8978921268</t>
-        </is>
-      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -24602,11 +21739,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H576" t="inlineStr">
-        <is>
-          <t>6300929220</t>
-        </is>
-      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -24644,11 +21776,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H577" t="inlineStr">
-        <is>
-          <t>9963233452</t>
-        </is>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -24686,11 +21813,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H578" t="inlineStr">
-        <is>
-          <t>9949086787</t>
-        </is>
-      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -24728,11 +21850,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H579" t="inlineStr">
-        <is>
-          <t>7893862886</t>
-        </is>
-      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -24770,11 +21887,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H580" t="inlineStr">
-        <is>
-          <t>9014387214</t>
-        </is>
-      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -24812,11 +21924,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H581" t="inlineStr">
-        <is>
-          <t>9989327833</t>
-        </is>
-      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -24854,11 +21961,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H582" t="inlineStr">
-        <is>
-          <t>8179961332</t>
-        </is>
-      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -24896,11 +21998,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H583" t="inlineStr">
-        <is>
-          <t>9492289549</t>
-        </is>
-      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -24938,11 +22035,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H584" t="inlineStr">
-        <is>
-          <t>8008492759</t>
-        </is>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -24980,11 +22072,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H585" t="inlineStr">
-        <is>
-          <t>9440990722</t>
-        </is>
-      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -25022,11 +22109,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H586" t="inlineStr">
-        <is>
-          <t>9182903970</t>
-        </is>
-      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -25064,11 +22146,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H587" t="inlineStr">
-        <is>
-          <t>7660096368</t>
-        </is>
-      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -25106,11 +22183,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H588" t="inlineStr">
-        <is>
-          <t>8328412768</t>
-        </is>
-      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -25148,11 +22220,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H589" t="inlineStr">
-        <is>
-          <t>9440436156</t>
-        </is>
-      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -25190,11 +22257,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H590" t="inlineStr">
-        <is>
-          <t>9440831982</t>
-        </is>
-      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -25232,11 +22294,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H591" t="inlineStr">
-        <is>
-          <t>9441640211</t>
-        </is>
-      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -25274,11 +22331,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H592" t="inlineStr">
-        <is>
-          <t>9885752639</t>
-        </is>
-      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -25316,11 +22368,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H593" t="inlineStr">
-        <is>
-          <t>9491310774</t>
-        </is>
-      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -25358,11 +22405,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H594" t="inlineStr">
-        <is>
-          <t>9701486740</t>
-        </is>
-      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -25400,11 +22442,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H595" t="inlineStr">
-        <is>
-          <t>9866859531</t>
-        </is>
-      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -25442,11 +22479,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H596" t="inlineStr">
-        <is>
-          <t>9492086277</t>
-        </is>
-      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -25484,11 +22516,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H597" t="inlineStr">
-        <is>
-          <t>8688229271</t>
-        </is>
-      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -25526,11 +22553,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H598" t="inlineStr">
-        <is>
-          <t>8074020084</t>
-        </is>
-      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -25568,11 +22590,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H599" t="inlineStr">
-        <is>
-          <t>7569521318</t>
-        </is>
-      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -25610,11 +22627,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H600" t="inlineStr">
-        <is>
-          <t>9912767820</t>
-        </is>
-      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -25652,11 +22664,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H601" t="inlineStr">
-        <is>
-          <t>9908110230</t>
-        </is>
-      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -25694,11 +22701,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H602" t="inlineStr">
-        <is>
-          <t>7382902369</t>
-        </is>
-      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -25736,11 +22738,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H603" t="inlineStr">
-        <is>
-          <t>8978771345</t>
-        </is>
-      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -25778,11 +22775,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H604" t="inlineStr">
-        <is>
-          <t>9948216667</t>
-        </is>
-      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -25820,11 +22812,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H605" t="inlineStr">
-        <is>
-          <t>9133630389</t>
-        </is>
-      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -25862,11 +22849,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H606" t="inlineStr">
-        <is>
-          <t>990829895</t>
-        </is>
-      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -25904,11 +22886,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H607" t="inlineStr">
-        <is>
-          <t>8919868679</t>
-        </is>
-      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -25946,11 +22923,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H608" t="inlineStr">
-        <is>
-          <t>9391256118</t>
-        </is>
-      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -25988,11 +22960,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H609" t="inlineStr">
-        <is>
-          <t>7093235079</t>
-        </is>
-      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -26030,11 +22997,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H610" t="inlineStr">
-        <is>
-          <t>9949634243</t>
-        </is>
-      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -26072,11 +23034,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H611" t="inlineStr">
-        <is>
-          <t>9490077725</t>
-        </is>
-      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -26114,11 +23071,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H612" t="inlineStr">
-        <is>
-          <t>8106070668</t>
-        </is>
-      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -26156,11 +23108,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H613" t="inlineStr">
-        <is>
-          <t>9951595977</t>
-        </is>
-      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -26198,11 +23145,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H614" t="inlineStr">
-        <is>
-          <t>7661822994</t>
-        </is>
-      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -26240,11 +23182,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H615" t="inlineStr">
-        <is>
-          <t>9247970655</t>
-        </is>
-      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -26282,11 +23219,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H616" t="inlineStr">
-        <is>
-          <t>8919325426</t>
-        </is>
-      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -26324,11 +23256,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H617" t="inlineStr">
-        <is>
-          <t>9494549853</t>
-        </is>
-      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -26366,11 +23293,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H618" t="inlineStr">
-        <is>
-          <t>7842418768</t>
-        </is>
-      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -26408,11 +23330,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr">
-        <is>
-          <t>9989935372</t>
-        </is>
-      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -26450,11 +23367,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H620" t="inlineStr">
-        <is>
-          <t>9989763127</t>
-        </is>
-      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -26492,11 +23404,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H621" t="inlineStr">
-        <is>
-          <t>9701644336</t>
-        </is>
-      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -26534,11 +23441,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H622" t="inlineStr">
-        <is>
-          <t>9014833319</t>
-        </is>
-      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -26576,11 +23478,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H623" t="inlineStr">
-        <is>
-          <t>9652798119</t>
-        </is>
-      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -26618,11 +23515,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H624" t="inlineStr">
-        <is>
-          <t>9000348634</t>
-        </is>
-      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -26660,7 +23552,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -26698,11 +23589,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H626" t="inlineStr">
-        <is>
-          <t>9553021211</t>
-        </is>
-      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -26740,11 +23626,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H627" t="inlineStr">
-        <is>
-          <t>9676378382</t>
-        </is>
-      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -26782,11 +23663,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H628" t="inlineStr">
-        <is>
-          <t>9885619502</t>
-        </is>
-      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -26824,11 +23700,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H629" t="inlineStr">
-        <is>
-          <t>8978911943</t>
-        </is>
-      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -26866,11 +23737,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H630" t="inlineStr">
-        <is>
-          <t>8919111200</t>
-        </is>
-      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -26908,11 +23774,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H631" t="inlineStr">
-        <is>
-          <t>8985620490</t>
-        </is>
-      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -26950,11 +23811,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H632" t="inlineStr">
-        <is>
-          <t>9573262690</t>
-        </is>
-      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -26992,11 +23848,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H633" t="inlineStr">
-        <is>
-          <t>9440713139</t>
-        </is>
-      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -27034,11 +23885,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H634" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -27076,11 +23922,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr">
-        <is>
-          <t>9493376483</t>
-        </is>
-      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -27118,11 +23959,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr">
-        <is>
-          <t>9705874396</t>
-        </is>
-      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -27160,11 +23996,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H637" t="inlineStr">
-        <is>
-          <t>8463931986</t>
-        </is>
-      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -27202,11 +24033,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr">
-        <is>
-          <t>9441523485</t>
-        </is>
-      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -27244,11 +24070,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H639" t="inlineStr">
-        <is>
-          <t>7842738146</t>
-        </is>
-      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -27286,11 +24107,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr">
-        <is>
-          <t>9490836055</t>
-        </is>
-      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -27328,11 +24144,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H641" t="inlineStr">
-        <is>
-          <t>9705850375</t>
-        </is>
-      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -27370,11 +24181,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H642" t="inlineStr">
-        <is>
-          <t>9704070561</t>
-        </is>
-      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -27412,11 +24218,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H643" t="inlineStr">
-        <is>
-          <t>7981952985</t>
-        </is>
-      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -27454,11 +24255,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H644" t="inlineStr">
-        <is>
-          <t>8008908818</t>
-        </is>
-      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -27496,11 +24292,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H645" t="inlineStr">
-        <is>
-          <t>8978206638</t>
-        </is>
-      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -27538,11 +24329,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr">
-        <is>
-          <t>9848867795</t>
-        </is>
-      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -27580,11 +24366,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H647" t="inlineStr">
-        <is>
-          <t>9032478407</t>
-        </is>
-      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -27622,11 +24403,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H648" t="inlineStr">
-        <is>
-          <t>7680856780</t>
-        </is>
-      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -27664,11 +24440,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H649" t="inlineStr">
-        <is>
-          <t>9515450619</t>
-        </is>
-      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -27706,11 +24477,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H650" t="inlineStr">
-        <is>
-          <t>9491343023</t>
-        </is>
-      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -27748,11 +24514,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H651" t="inlineStr">
-        <is>
-          <t>9912012554</t>
-        </is>
-      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -27790,11 +24551,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H652" t="inlineStr">
-        <is>
-          <t>9640648427</t>
-        </is>
-      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -27832,11 +24588,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H653" t="inlineStr">
-        <is>
-          <t>7695996530</t>
-        </is>
-      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -27874,11 +24625,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H654" t="inlineStr">
-        <is>
-          <t>8919215242</t>
-        </is>
-      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -27916,11 +24662,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H655" t="inlineStr">
-        <is>
-          <t>9912434954</t>
-        </is>
-      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -27958,11 +24699,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H656" t="inlineStr">
-        <is>
-          <t>8125623572</t>
-        </is>
-      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -28000,11 +24736,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H657" t="inlineStr">
-        <is>
-          <t>7901023806</t>
-        </is>
-      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -28042,11 +24773,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H658" t="inlineStr">
-        <is>
-          <t>9440729045</t>
-        </is>
-      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -28084,11 +24810,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H659" t="inlineStr">
-        <is>
-          <t>8985671631</t>
-        </is>
-      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -28126,11 +24847,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H660" t="inlineStr">
-        <is>
-          <t>9666545435</t>
-        </is>
-      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -28168,11 +24884,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H661" t="inlineStr">
-        <is>
-          <t>9908905657</t>
-        </is>
-      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -28210,11 +24921,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H662" t="inlineStr">
-        <is>
-          <t>8919113411</t>
-        </is>
-      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -28252,11 +24958,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H663" t="inlineStr">
-        <is>
-          <t>9493120974</t>
-        </is>
-      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -28294,11 +24995,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H664" t="inlineStr">
-        <is>
-          <t>9676425393</t>
-        </is>
-      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -28336,11 +25032,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H665" t="inlineStr">
-        <is>
-          <t>9849247022</t>
-        </is>
-      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -28378,11 +25069,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H666" t="inlineStr">
-        <is>
-          <t>9550562630</t>
-        </is>
-      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -28420,11 +25106,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H667" t="inlineStr">
-        <is>
-          <t>7382897649</t>
-        </is>
-      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -28462,11 +25143,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H668" t="inlineStr">
-        <is>
-          <t>7337542585</t>
-        </is>
-      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -28504,11 +25180,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H669" t="inlineStr">
-        <is>
-          <t>9346681126</t>
-        </is>
-      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -28546,11 +25217,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H670" t="inlineStr">
-        <is>
-          <t>9951185813</t>
-        </is>
-      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -28588,11 +25254,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H671" t="inlineStr">
-        <is>
-          <t>8340877647</t>
-        </is>
-      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -28630,11 +25291,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H672" t="inlineStr">
-        <is>
-          <t>8639977124</t>
-        </is>
-      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -28672,11 +25328,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H673" t="inlineStr">
-        <is>
-          <t>9959535335</t>
-        </is>
-      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -28714,11 +25365,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H674" t="inlineStr">
-        <is>
-          <t>9949047007</t>
-        </is>
-      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -28756,11 +25402,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H675" t="inlineStr">
-        <is>
-          <t>9848180206</t>
-        </is>
-      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -28798,11 +25439,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H676" t="inlineStr">
-        <is>
-          <t>8340903870</t>
-        </is>
-      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -28840,11 +25476,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H677" t="inlineStr">
-        <is>
-          <t>7382891887</t>
-        </is>
-      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -28882,7 +25513,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -28920,11 +25550,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H679" t="inlineStr">
-        <is>
-          <t>9494680049</t>
-        </is>
-      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -28962,11 +25587,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H680" t="inlineStr">
-        <is>
-          <t>950237529</t>
-        </is>
-      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -29004,11 +25624,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H681" t="inlineStr">
-        <is>
-          <t>9705415553</t>
-        </is>
-      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -29046,11 +25661,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H682" t="inlineStr">
-        <is>
-          <t>9492219286</t>
-        </is>
-      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -29088,11 +25698,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H683" t="inlineStr">
-        <is>
-          <t>9866272545</t>
-        </is>
-      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -29130,11 +25735,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H684" t="inlineStr">
-        <is>
-          <t>9618835349</t>
-        </is>
-      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -29172,11 +25772,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H685" t="inlineStr">
-        <is>
-          <t>9030160116</t>
-        </is>
-      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -29214,11 +25809,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H686" t="inlineStr">
-        <is>
-          <t>9912894431</t>
-        </is>
-      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -29256,11 +25846,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H687" t="inlineStr">
-        <is>
-          <t>8106113283</t>
-        </is>
-      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -29298,11 +25883,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H688" t="inlineStr">
-        <is>
-          <t>7095852458</t>
-        </is>
-      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -29340,11 +25920,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H689" t="inlineStr">
-        <is>
-          <t>9505102616</t>
-        </is>
-      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -29382,11 +25957,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H690" t="inlineStr">
-        <is>
-          <t>9490475253</t>
-        </is>
-      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -29424,11 +25994,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H691" t="inlineStr">
-        <is>
-          <t>9949619489</t>
-        </is>
-      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -29466,11 +26031,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H692" t="inlineStr">
-        <is>
-          <t>8919468738</t>
-        </is>
-      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -29508,11 +26068,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H693" t="inlineStr">
-        <is>
-          <t>9948482236</t>
-        </is>
-      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -29550,11 +26105,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H694" t="inlineStr">
-        <is>
-          <t>7995225334</t>
-        </is>
-      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -29592,11 +26142,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H695" t="inlineStr">
-        <is>
-          <t>9072903943</t>
-        </is>
-      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -29634,11 +26179,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H696" t="inlineStr">
-        <is>
-          <t>6301848636</t>
-        </is>
-      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -29676,11 +26216,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H697" t="inlineStr">
-        <is>
-          <t>9866515241</t>
-        </is>
-      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -29718,11 +26253,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H698" t="inlineStr">
-        <is>
-          <t>9392845126</t>
-        </is>
-      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -29760,11 +26290,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H699" t="inlineStr">
-        <is>
-          <t>9640122214</t>
-        </is>
-      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -29802,11 +26327,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H700" t="inlineStr">
-        <is>
-          <t>9441003137</t>
-        </is>
-      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -29844,11 +26364,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H701" t="inlineStr">
-        <is>
-          <t>9701510482</t>
-        </is>
-      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -29886,11 +26401,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H702" t="inlineStr">
-        <is>
-          <t>7893441212</t>
-        </is>
-      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -29928,11 +26438,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H703" t="inlineStr">
-        <is>
-          <t>9951813483</t>
-        </is>
-      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -29970,11 +26475,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H704" t="inlineStr">
-        <is>
-          <t>7286824899</t>
-        </is>
-      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -30012,11 +26512,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H705" t="inlineStr">
-        <is>
-          <t>7893953332</t>
-        </is>
-      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -30054,11 +26549,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H706" t="inlineStr">
-        <is>
-          <t>7702173571</t>
-        </is>
-      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -30096,11 +26586,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H707" t="inlineStr">
-        <is>
-          <t>6281847699</t>
-        </is>
-      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -30138,11 +26623,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H708" t="inlineStr">
-        <is>
-          <t>9603587813</t>
-        </is>
-      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -30180,11 +26660,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H709" t="inlineStr">
-        <is>
-          <t>8464895384</t>
-        </is>
-      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -30222,11 +26697,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H710" t="inlineStr">
-        <is>
-          <t>9849614610</t>
-        </is>
-      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -30264,11 +26734,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H711" t="inlineStr">
-        <is>
-          <t>6309429668</t>
-        </is>
-      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -30306,11 +26771,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H712" t="inlineStr">
-        <is>
-          <t>9949714648</t>
-        </is>
-      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -30348,11 +26808,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H713" t="inlineStr">
-        <is>
-          <t>9701925135</t>
-        </is>
-      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -30390,11 +26845,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H714" t="inlineStr">
-        <is>
-          <t>9676673827</t>
-        </is>
-      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -30432,11 +26882,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H715" t="inlineStr">
-        <is>
-          <t>7569362300</t>
-        </is>
-      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -30474,11 +26919,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H716" t="inlineStr">
-        <is>
-          <t>9912511851</t>
-        </is>
-      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -30516,11 +26956,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H717" t="inlineStr">
-        <is>
-          <t>9492218220</t>
-        </is>
-      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -30558,11 +26993,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H718" t="inlineStr">
-        <is>
-          <t>8790804249</t>
-        </is>
-      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -30600,11 +27030,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H719" t="inlineStr">
-        <is>
-          <t>8978304844</t>
-        </is>
-      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -30642,11 +27067,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H720" t="inlineStr">
-        <is>
-          <t>9444669338</t>
-        </is>
-      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -30684,11 +27104,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H721" t="inlineStr">
-        <is>
-          <t>9030592066</t>
-        </is>
-      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -30726,11 +27141,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H722" t="inlineStr">
-        <is>
-          <t>8465909274</t>
-        </is>
-      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -30768,11 +27178,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H723" t="inlineStr">
-        <is>
-          <t>8374326946</t>
-        </is>
-      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -30810,11 +27215,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H724" t="inlineStr">
-        <is>
-          <t>9347378745</t>
-        </is>
-      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -30852,11 +27252,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H725" t="inlineStr">
-        <is>
-          <t>7893529929</t>
-        </is>
-      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -30894,11 +27289,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H726" t="inlineStr">
-        <is>
-          <t>9100450511</t>
-        </is>
-      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -30936,11 +27326,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H727" t="inlineStr">
-        <is>
-          <t>9676369586</t>
-        </is>
-      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -30978,11 +27363,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H728" t="inlineStr">
-        <is>
-          <t>9492122646</t>
-        </is>
-      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -31020,11 +27400,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H729" t="inlineStr">
-        <is>
-          <t>9959104021</t>
-        </is>
-      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -31062,11 +27437,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H730" t="inlineStr">
-        <is>
-          <t>9182951802</t>
-        </is>
-      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -31104,11 +27474,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H731" t="inlineStr">
-        <is>
-          <t>9849939771</t>
-        </is>
-      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -31146,11 +27511,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H732" t="inlineStr">
-        <is>
-          <t>9701136002</t>
-        </is>
-      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -31188,11 +27548,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H733" t="inlineStr">
-        <is>
-          <t>6305115662</t>
-        </is>
-      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -31230,11 +27585,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H734" t="inlineStr">
-        <is>
-          <t>9121961871</t>
-        </is>
-      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -31272,11 +27622,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H735" t="inlineStr">
-        <is>
-          <t>9652259411</t>
-        </is>
-      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -31314,11 +27659,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H736" t="inlineStr">
-        <is>
-          <t>7780745797</t>
-        </is>
-      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -31356,11 +27696,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H737" t="inlineStr">
-        <is>
-          <t>9398987127</t>
-        </is>
-      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -31398,11 +27733,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H738" t="inlineStr">
-        <is>
-          <t>9491757848</t>
-        </is>
-      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -31440,11 +27770,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H739" t="inlineStr">
-        <is>
-          <t>9912514554</t>
-        </is>
-      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -31482,11 +27807,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H740" t="inlineStr">
-        <is>
-          <t>8985631634</t>
-        </is>
-      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -31524,11 +27844,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H741" t="inlineStr">
-        <is>
-          <t>9849178925</t>
-        </is>
-      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -31566,11 +27881,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H742" t="inlineStr">
-        <is>
-          <t>7337266652</t>
-        </is>
-      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -31608,11 +27918,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H743" t="inlineStr">
-        <is>
-          <t>8499896762</t>
-        </is>
-      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -31650,11 +27955,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H744" t="inlineStr">
-        <is>
-          <t>9908235018</t>
-        </is>
-      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -31692,11 +27992,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H745" t="inlineStr">
-        <is>
-          <t>9550671630</t>
-        </is>
-      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -31734,11 +28029,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H746" t="inlineStr">
-        <is>
-          <t>8637481749</t>
-        </is>
-      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -31776,11 +28066,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H747" t="inlineStr">
-        <is>
-          <t>9502400565</t>
-        </is>
-      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -31818,11 +28103,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H748" t="inlineStr">
-        <is>
-          <t>9381864241</t>
-        </is>
-      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -31860,11 +28140,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H749" t="inlineStr">
-        <is>
-          <t>9347378745</t>
-        </is>
-      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -31902,11 +28177,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H750" t="inlineStr">
-        <is>
-          <t>9603880214</t>
-        </is>
-      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -31944,11 +28214,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H751" t="inlineStr">
-        <is>
-          <t>9494414403</t>
-        </is>
-      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -31986,11 +28251,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H752" t="inlineStr">
-        <is>
-          <t>7416861917</t>
-        </is>
-      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -32028,11 +28288,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H753" t="inlineStr">
-        <is>
-          <t>9108291686</t>
-        </is>
-      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -32070,11 +28325,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H754" t="inlineStr">
-        <is>
-          <t>9581922933</t>
-        </is>
-      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -32112,11 +28362,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H755" t="inlineStr">
-        <is>
-          <t>9989676937</t>
-        </is>
-      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -32154,11 +28399,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H756" t="inlineStr">
-        <is>
-          <t>8790474600</t>
-        </is>
-      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -32196,11 +28436,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H757" t="inlineStr">
-        <is>
-          <t>7095720787</t>
-        </is>
-      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -32238,11 +28473,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H758" t="inlineStr">
-        <is>
-          <t>7659943830</t>
-        </is>
-      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -32280,11 +28510,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H759" t="inlineStr">
-        <is>
-          <t>9849828562</t>
-        </is>
-      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -32322,11 +28547,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H760" t="inlineStr">
-        <is>
-          <t>9441269510</t>
-        </is>
-      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -32364,11 +28584,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H761" t="inlineStr">
-        <is>
-          <t>9000028903</t>
-        </is>
-      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -32406,11 +28621,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H762" t="inlineStr">
-        <is>
-          <t>9703825894</t>
-        </is>
-      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -32448,11 +28658,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H763" t="inlineStr">
-        <is>
-          <t>8939729715</t>
-        </is>
-      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -32490,11 +28695,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H764" t="inlineStr">
-        <is>
-          <t>8522964357</t>
-        </is>
-      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -32532,11 +28732,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H765" t="inlineStr">
-        <is>
-          <t>9550554360</t>
-        </is>
-      </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -32574,11 +28769,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H766" t="inlineStr">
-        <is>
-          <t>9347777986</t>
-        </is>
-      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -32616,11 +28806,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H767" t="inlineStr">
-        <is>
-          <t>8297834476</t>
-        </is>
-      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -32658,11 +28843,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H768" t="inlineStr">
-        <is>
-          <t>8886464766</t>
-        </is>
-      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -32700,11 +28880,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H769" t="inlineStr">
-        <is>
-          <t>9346294220</t>
-        </is>
-      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -32742,11 +28917,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H770" t="inlineStr">
-        <is>
-          <t>9440831445</t>
-        </is>
-      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -32784,11 +28954,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H771" t="inlineStr">
-        <is>
-          <t>7013808702</t>
-        </is>
-      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -32826,11 +28991,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H772" t="inlineStr">
-        <is>
-          <t>6302597254</t>
-        </is>
-      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -32868,11 +29028,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H773" t="inlineStr">
-        <is>
-          <t>7993173962</t>
-        </is>
-      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -32910,11 +29065,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H774" t="inlineStr">
-        <is>
-          <t>9700478722</t>
-        </is>
-      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -32952,11 +29102,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H775" t="inlineStr">
-        <is>
-          <t>9704477698</t>
-        </is>
-      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -32994,11 +29139,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H776" t="inlineStr">
-        <is>
-          <t>7893879283</t>
-        </is>
-      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -33036,11 +29176,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H777" t="inlineStr">
-        <is>
-          <t>9912943409</t>
-        </is>
-      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -33078,11 +29213,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H778" t="inlineStr">
-        <is>
-          <t>6303083736</t>
-        </is>
-      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -33120,11 +29250,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H779" t="inlineStr">
-        <is>
-          <t>9640321438</t>
-        </is>
-      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -33162,11 +29287,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H780" t="inlineStr">
-        <is>
-          <t>9177644280</t>
-        </is>
-      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -33204,11 +29324,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H781" t="inlineStr">
-        <is>
-          <t>9441417114</t>
-        </is>
-      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -33246,11 +29361,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H782" t="inlineStr">
-        <is>
-          <t>6302009142</t>
-        </is>
-      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -33288,11 +29398,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H783" t="inlineStr">
-        <is>
-          <t>8328619397</t>
-        </is>
-      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -33330,11 +29435,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H784" t="inlineStr">
-        <is>
-          <t>8309145856</t>
-        </is>
-      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -33372,11 +29472,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H785" t="inlineStr">
-        <is>
-          <t>9052558561</t>
-        </is>
-      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -33414,11 +29509,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H786" t="inlineStr">
-        <is>
-          <t>9573530076</t>
-        </is>
-      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -33456,11 +29546,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H787" t="inlineStr">
-        <is>
-          <t>9491114862</t>
-        </is>
-      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -33498,11 +29583,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H788" t="inlineStr">
-        <is>
-          <t>9121586988</t>
-        </is>
-      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -33540,11 +29620,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H789" t="inlineStr">
-        <is>
-          <t>9966044154</t>
-        </is>
-      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -33582,11 +29657,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H790" t="inlineStr">
-        <is>
-          <t>9121638002</t>
-        </is>
-      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -33624,11 +29694,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H791" t="inlineStr">
-        <is>
-          <t>9390652484</t>
-        </is>
-      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -33666,11 +29731,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H792" t="inlineStr">
-        <is>
-          <t>7386486745</t>
-        </is>
-      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -33708,11 +29768,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H793" t="inlineStr">
-        <is>
-          <t>8297395944</t>
-        </is>
-      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -33750,11 +29805,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H794" t="inlineStr">
-        <is>
-          <t>9493031213</t>
-        </is>
-      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -33792,11 +29842,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H795" t="inlineStr">
-        <is>
-          <t>8555015727</t>
-        </is>
-      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -33834,11 +29879,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H796" t="inlineStr">
-        <is>
-          <t>7032560401</t>
-        </is>
-      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -33876,11 +29916,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H797" t="inlineStr">
-        <is>
-          <t>6302979638</t>
-        </is>
-      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -33918,11 +29953,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H798" t="inlineStr">
-        <is>
-          <t>9347355152</t>
-        </is>
-      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -33960,11 +29990,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H799" t="inlineStr">
-        <is>
-          <t>9550698268</t>
-        </is>
-      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -34002,11 +30027,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H800" t="inlineStr">
-        <is>
-          <t>9010704495</t>
-        </is>
-      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -34044,11 +30064,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H801" t="inlineStr">
-        <is>
-          <t>9640219850</t>
-        </is>
-      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -34086,11 +30101,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H802" t="inlineStr">
-        <is>
-          <t>9346403440</t>
-        </is>
-      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -34128,11 +30138,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H803" t="inlineStr">
-        <is>
-          <t>9502507978</t>
-        </is>
-      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -34170,11 +30175,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H804" t="inlineStr">
-        <is>
-          <t>9959452210</t>
-        </is>
-      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -34212,11 +30212,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H805" t="inlineStr">
-        <is>
-          <t>9441951995</t>
-        </is>
-      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -34254,11 +30249,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H806" t="inlineStr">
-        <is>
-          <t>9392411868</t>
-        </is>
-      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -34296,11 +30286,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H807" t="inlineStr">
-        <is>
-          <t>8367494147</t>
-        </is>
-      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -34338,11 +30323,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H808" t="inlineStr">
-        <is>
-          <t>9491734218</t>
-        </is>
-      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -34380,11 +30360,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H809" t="inlineStr">
-        <is>
-          <t>9133817945</t>
-        </is>
-      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -34422,11 +30397,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H810" t="inlineStr">
-        <is>
-          <t>8790640759</t>
-        </is>
-      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -34464,11 +30434,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H811" t="inlineStr">
-        <is>
-          <t>9849220910</t>
-        </is>
-      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -34506,11 +30471,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H812" t="inlineStr">
-        <is>
-          <t>9866782578</t>
-        </is>
-      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -34548,11 +30508,6 @@
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="H813" t="inlineStr">
-        <is>
-          <t>7993588920</t>
-        </is>
-      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -34588,11 +30543,6 @@
       <c r="G814" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="H814" t="inlineStr">
-        <is>
-          <t>8555866493</t>
         </is>
       </c>
     </row>
